--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_baseline_enriched.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_baseline_enriched.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">display_label</t>
   </si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Mode of Delivery</t>
   </si>
   <si>
-    <t xml:space="preserve">Outcome</t>
+    <t xml:space="preserve">Outcome at discharge</t>
   </si>
   <si>
     <t xml:space="preserve">Head Circumference (cm)</t>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mode of delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome</t>
   </si>
   <si>
     <t xml:space="preserve">Maternal parity (the number of times a mother has given birth to a fetus with a gestational age of 24 weeks or more, regardless of whether the child was born alive or was stillborn.)</t>
@@ -706,25 +709,25 @@
         <v>33</v>
       </c>
       <c r="AB1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AE1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -805,22 +808,22 @@
         <v>34</v>
       </c>
       <c r="AB2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD2" t="s">
         <v>28</v>
       </c>
       <c r="AE2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH2" t="b">
         <v>1</v>
@@ -908,13 +911,13 @@
         <v>2</v>
       </c>
       <c r="AB3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC3" t="s">
         <v>28</v>
       </c>
       <c r="AD3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AE3" t="s">
         <v>28</v>
@@ -1011,13 +1014,13 @@
         <v>35</v>
       </c>
       <c r="AB4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC4" t="s">
         <v>28</v>
       </c>
       <c r="AD4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AE4" t="s">
         <v>28</v>
@@ -1110,7 +1113,7 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC5" t="s">
         <v>28</v>
@@ -1207,7 +1210,7 @@
         <v>37</v>
       </c>
       <c r="AB6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="s">
         <v>28</v>
@@ -1222,7 +1225,7 @@
         <v>28</v>
       </c>
       <c r="AG6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH6" t="b">
         <v>1</v>
@@ -1307,7 +1310,7 @@
         <v>28</v>
       </c>
       <c r="AC7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD7" t="s">
         <v>28</v>
@@ -1510,10 +1513,10 @@
         <v>39</v>
       </c>
       <c r="AB9" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC9" t="s">
         <v>53</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>52</v>
       </c>
       <c r="AD9" t="s">
         <v>28</v>
@@ -1695,7 +1698,7 @@
         <v>40</v>
       </c>
       <c r="AB11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC11" t="s">
         <v>28</v>
@@ -1804,7 +1807,7 @@
         <v>28</v>
       </c>
       <c r="AD12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE12" t="s">
         <v>28</v>
@@ -1813,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="AG12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AH12" t="b">
         <v>1</v>
@@ -1901,7 +1904,7 @@
         <v>11</v>
       </c>
       <c r="AB13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC13" t="s">
         <v>28</v>
@@ -2000,10 +2003,10 @@
         <v>41</v>
       </c>
       <c r="AB14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD14" t="s">
         <v>28</v>
@@ -2198,7 +2201,7 @@
         <v>42</v>
       </c>
       <c r="AB16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC16" t="s">
         <v>28</v>
@@ -2297,7 +2300,7 @@
         <v>43</v>
       </c>
       <c r="AB17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC17" t="s">
         <v>28</v>
@@ -2346,7 +2349,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2393,10 +2396,10 @@
         <v>1</v>
       </c>
       <c r="AA18" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC18" t="s">
         <v>28</v>
@@ -2411,7 +2414,7 @@
         <v>28</v>
       </c>
       <c r="AG18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH18" t="b">
         <v>1</v>
@@ -2505,7 +2508,7 @@
         <v>28</v>
       </c>
       <c r="AD19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE19" t="s">
         <v>28</v>
@@ -2514,7 +2517,7 @@
         <v>28</v>
       </c>
       <c r="AG19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH19" t="b">
         <v>1</v>
@@ -2599,16 +2602,16 @@
       </c>
       <c r="Z20"/>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC20" t="s">
         <v>28</v>
       </c>
       <c r="AD20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AE20" t="s">
         <v>28</v>
@@ -2695,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="Z21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC21" t="s">
         <v>28</v>
@@ -2797,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="AA22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AD22" t="s">
         <v>28</v>
@@ -2995,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="AA24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="s">
         <v>28</v>
@@ -3107,7 +3110,7 @@
         <v>28</v>
       </c>
       <c r="AD25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE25" t="s">
         <v>28</v>
@@ -3197,10 +3200,10 @@
         <v>1</v>
       </c>
       <c r="AA26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC26" t="s">
         <v>28</v>
@@ -3494,6 +3497,174 @@
         <v>28</v>
       </c>
       <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Maternal age (years) -- canonical (derived)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>60</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Derived canonical maternal age in years. Cleaning pipeline Module 15 computes coalesce(matageyrs, mat_age_date_years). ZIM captures matageyrs only (matagedate is a Malawi maternity-form field), so in ZIM data this column always equals matageyrs and mat_age_source is always 'matageyrs'; the shared derivation keeps the two countries on one schema. Emitted only where a source column is present. Originals retained. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3793,7 +3964,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Birth Asphyxia/ Hypoxic Ischaemic Encephalopathy (HIE)</t>
+          <t>Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4153,7 +4324,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Congenital Dislocation of the hip (CDH)</t>
+          <t>Congenital dislocation of the hip (CDH)</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4483,7 +4654,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Risk factors for sepsis (but sepsis ruled out)</t>
+          <t>Sepsis (risk factors, but ruled out)</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4513,7 +4684,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mild Talipes (club foot)</t>
+          <t>Talipes MILD (club foot)</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -4903,7 +5074,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Term with RD</t>
+          <t>Respiratory Distress (term baby)</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5113,7 +5284,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (Symptomatic)</t>
+          <t>Hypoglycaemia (symptomatic)</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -5173,7 +5344,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Physiological Jaundice</t>
+          <t>Jaundice (physiological)</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5413,7 +5584,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Very Premature (28-31 weeks)</t>
+          <t>Very Premature (28 to 31.6 weeks)</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -5503,7 +5674,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pathological Jaundice</t>
+          <t>Jaundice (pathological)</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5558,12 +5729,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>ProJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prolonged Jaundice</t>
+          <t>Jaundice (prolonged)</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -5576,7 +5747,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>ProJ</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5939,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>PJaundice</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>Prolonged Jaundice (babies from 21 days of age)</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5781,12 +5952,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>b30ef9d1-024b-45d8-bcc8-c9ef3331f644</t>
+          <t>947d944e-bc0b-4cf8-be4c-fdff56035020</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Premature</t>
+          <t>PJaundice</t>
         </is>
       </c>
     </row>
@@ -5798,12 +5969,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Syph_Exp</t>
+          <t>Premature</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Syphilis exposed</t>
+          <t>Premature</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5811,42 +5982,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>bbbad131-9323-4f6e-9200-ca640bb5bf27</t>
+          <t>b30ef9d1-024b-45d8-bcc8-c9ef3331f644</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Syph_Exp</t>
+          <t>Premature</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>diagdis1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Syph_Exp</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Syphilis exposed</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5577b2a8-f2f9-4d63-8c8e-0a330677b709</t>
+          <t>bbbad131-9323-4f6e-9200-ca640bb5bf27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Syph_Exp</t>
         </is>
       </c>
     </row>
@@ -5858,25 +6029,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0560751e-e423-43af-ab3f-36f49ca1f4a1</t>
+          <t>5577b2a8-f2f9-4d63-8c8e-0a330677b709</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -5888,25 +6059,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Not Sure</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>043061ae-ba3e-420e-bc7c-07ea11d6712d</t>
+          <t>0560751e-e423-43af-ab3f-36f49ca1f4a1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5918,25 +6089,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Unsure</t>
+          <t>Not Sure</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3d7a5b87-2617-4f75-8963-dbbe741f5e0a</t>
+          <t>043061ae-ba3e-420e-bc7c-07ea11d6712d</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -5948,55 +6119,55 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AmbG</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ambiguous genitalia</t>
+          <t>Unsure</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>a8aa85ec-beeb-4b4d-92ad-387ae869f97d</t>
+          <t>3d7a5b87-2617-4f75-8963-dbbe741f5e0a</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AmbG</t>
+          <t>U</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>medsdis</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>AmbG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Ambiguous genitalia</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>a8aa85ec-beeb-4b4d-92ad-387ae869f97d</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>AmbG</t>
         </is>
       </c>
     </row>
@@ -6008,25 +6179,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Folic acid</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>7c699351-2764-4d66-abde-06b29e90d8cb</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -6038,25 +6209,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iron (Ferrous sulphate)</t>
+          <t>Folic acid</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>58e83e70-6698-4b24-a43a-8b7e9b72c52b</t>
+          <t>7c699351-2764-4d66-abde-06b29e90d8cb</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -6068,25 +6239,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vitamin D</t>
+          <t>Iron (Ferrous sulphate)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
+          <t>58e83e70-6698-4b24-a43a-8b7e9b72c52b</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>FE</t>
         </is>
       </c>
     </row>
@@ -6098,25 +6269,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>VITD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Intramuscular procaine penicillin (syphillis)</t>
+          <t>Vitamin D</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>25878b06-3441-4b58-889c-ec5868fb7f0a</t>
+          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>VITD</t>
         </is>
       </c>
     </row>
@@ -6128,25 +6299,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NVP (Nevirapine)</t>
+          <t>Intramuscular procaine penicillin (syphillis)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5b7a2825-6bc4-4de3-9d9f-9358815b877d</t>
+          <t>25878b06-3441-4b58-889c-ec5868fb7f0a</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
@@ -6158,25 +6329,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Amoxicillin</t>
+          <t>NVP (Nevirapine)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
+          <t>5b7a2825-6bc4-4de3-9d9f-9358815b877d</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -6188,25 +6359,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>Amox</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AZT (Zidovudine)</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
+          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>Amox</t>
         </is>
       </c>
     </row>
@@ -6218,25 +6389,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>AZT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AZT (Zidovudine)</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>AZT</t>
         </is>
       </c>
     </row>
@@ -6248,25 +6419,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Amikacin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -6278,25 +6449,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amik</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amikacin</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7a841c62-62c0-4247-a141-68b5120b3cd9</t>
+          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Amik</t>
         </is>
       </c>
     </row>
@@ -6313,15 +6484,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BCG Vaccine</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
+          <t>7a841c62-62c0-4247-a141-68b5120b3cd9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6338,25 +6509,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>BCG Vaccine</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
+          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>BCG</t>
         </is>
       </c>
     </row>
@@ -6368,25 +6539,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cloxacillin</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>cff42224-f861-4330-9468-cdc903298e70</t>
+          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CAF</t>
         </is>
       </c>
     </row>
@@ -6398,25 +6569,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Clox</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Folate</t>
+          <t>Cloxacillin</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
+          <t>cff42224-f861-4330-9468-cdc903298e70</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Clox</t>
         </is>
       </c>
     </row>
@@ -6428,25 +6599,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Folate</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
+          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -6458,25 +6629,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metronidazole</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
+          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
@@ -6488,25 +6659,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nevirapine</t>
+          <t>Metronidazole</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
+          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -6518,25 +6689,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phenobarbitone</t>
+          <t>Nevirapine</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
+          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -6548,25 +6719,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>PHEN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Procaine Penicillin</t>
+          <t>Phenobarbitone</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
+          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>PHEN</t>
         </is>
       </c>
     </row>
@@ -6578,85 +6749,85 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine</t>
+          <t>Procaine Penicillin</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
+          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>medsgiven</t>
+          <t>medsdis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>TTV</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>X penicillin</t>
+          <t>Tetanus Vaccine</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0a98f906-82dc-4082-917b-4657a612566e</t>
+          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>TTV</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>medsgiven</t>
+          <t>medsdis</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>AZT3TC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gentamicin</t>
+          <t>Zidolam (AZT and 3TC)</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4f895d9a-7600-44c6-b867-c72af7bd7413</t>
+          <t>2f8946b7-668c-4eca-aef7-217c7378a4f3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>AZT3TC</t>
         </is>
       </c>
     </row>
@@ -6668,25 +6839,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>X-penicillin and gentamicin</t>
+          <t>X penicillin</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>27e4ad0e-ad3d-4ef1-97d0-7dfff0495574</t>
+          <t>0a98f906-82dc-4082-917b-4657a612566e</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>BP</t>
         </is>
       </c>
     </row>
@@ -6698,25 +6869,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BCG Vaccine</t>
+          <t>Gentamicin</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
+          <t>4f895d9a-7600-44c6-b867-c72af7bd7413</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Gent</t>
         </is>
       </c>
     </row>
@@ -6728,25 +6899,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>ABX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Amoxicillin</t>
+          <t>X-penicillin and gentamicin</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
+          <t>27e4ad0e-ad3d-4ef1-97d0-7dfff0495574</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amox</t>
+          <t>ABX</t>
         </is>
       </c>
     </row>
@@ -6758,25 +6929,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Amikacin</t>
+          <t>BCG Vaccine</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
+          <t>9ae22e77-c218-4063-adda-7ba4ebc6f535</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amik</t>
+          <t>BCG</t>
         </is>
       </c>
     </row>
@@ -6788,25 +6959,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMIN</t>
+          <t>Amox</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Aminophylline</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>b43e9922-debb-426b-9a29-5c8e55239813</t>
+          <t>98acd732-d1f8-4e3c-ba4e-32d7bf503e2d</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMIN</t>
+          <t>Amox</t>
         </is>
       </c>
     </row>
@@ -6818,25 +6989,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Amik</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ampicillin</t>
+          <t>Amikacin</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>8bf190f9-958d-40b8-850a-c98e816ab3b8</t>
+          <t>25d74b8a-5400-47a0-af41-4d798a086fef</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Amik</t>
         </is>
       </c>
     </row>
@@ -6848,25 +7019,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>AMIN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AZT (Zidovudine)</t>
+          <t>Aminophylline</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
+          <t>b43e9922-debb-426b-9a29-5c8e55239813</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AZT</t>
+          <t>AMIN</t>
         </is>
       </c>
     </row>
@@ -6878,25 +7049,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>Amp</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Ampicillin</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
+          <t>8bf190f9-958d-40b8-850a-c98e816ab3b8</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>Amp</t>
         </is>
       </c>
     </row>
@@ -6908,25 +7079,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>AZT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ceftriaxone</t>
+          <t>AZT (Zidovudine)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2c165a7b-374b-4364-b4dd-df8c48b8d3d7</t>
+          <t>a99d1306-3368-403d-b584-66a2b4baba96</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>AZT</t>
         </is>
       </c>
     </row>
@@ -6938,25 +7109,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHLO</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chloramphenicol</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>afd30972-9cec-46b8-93c8-86f9c225adc0</t>
+          <t>eb339a17-18ac-4b87-b12f-c69446711174</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CHLO</t>
+          <t>CAF</t>
         </is>
       </c>
     </row>
@@ -6968,25 +7139,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cloxacillin</t>
+          <t>Ceftriaxone</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>cff42224-f861-4330-9468-cdc903298e70</t>
+          <t>2c165a7b-374b-4364-b4dd-df8c48b8d3d7</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Clox</t>
+          <t>CEF</t>
         </is>
       </c>
     </row>
@@ -6998,25 +7169,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>CHLO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Folate</t>
+          <t>Chloramphenicol</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
+          <t>afd30972-9cec-46b8-93c8-86f9c225adc0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>CHLO</t>
         </is>
       </c>
     </row>
@@ -7028,25 +7199,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IMI</t>
+          <t>Clox</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Imipenem</t>
+          <t>Cloxacillin</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>9b23de8c-2e7f-4663-b504-9605d6b09c6f</t>
+          <t>cff42224-f861-4330-9468-cdc903298e70</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMI</t>
+          <t>Clox</t>
         </is>
       </c>
     </row>
@@ -7058,25 +7229,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Folate</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
+          <t>2f82e32b-cdb6-45b2-9e52-0d7173b1ffb4</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FOL</t>
         </is>
       </c>
     </row>
@@ -7088,25 +7259,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IMI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metronidazole</t>
+          <t>Imipenem</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
+          <t>9b23de8c-2e7f-4663-b504-9605d6b09c6f</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>IMI</t>
         </is>
       </c>
     </row>
@@ -7118,25 +7289,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nevirapine</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
+          <t>890d24d9-a685-42bc-8789-5dae0d5d4c5c</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
@@ -7148,25 +7319,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Phenobarbitone</t>
+          <t>Metronidazole</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
+          <t>b5129f76-b536-4eed-8b2b-b021630fe680</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PHEN</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -7178,25 +7349,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Procaine Penicillin</t>
+          <t>Nevirapine</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
+          <t>24927217-daa7-424b-a609-75fc5ec615ff</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PROC</t>
+          <t>NVP</t>
         </is>
       </c>
     </row>
@@ -7208,25 +7379,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PHEN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine</t>
+          <t>Phenobarbitone</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
+          <t>1ac18bf8-fdaa-497f-8d2c-3f35ff0bb002</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>PHEN</t>
         </is>
       </c>
     </row>
@@ -7238,25 +7409,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vancomycin</t>
+          <t>Procaine Penicillin</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2ca153c6-d678-445f-8ee1-a679c933737d</t>
+          <t>c89a65bb-667c-4e6f-90fe-68110bcad003</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>PROC</t>
         </is>
       </c>
     </row>
@@ -7268,25 +7439,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>TTV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vitamin D</t>
+          <t>Tetanus Vaccine</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
+          <t>c24e04c1-720e-4935-97a5-6ce0584e96e0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>VITD</t>
+          <t>TTV</t>
         </is>
       </c>
     </row>
@@ -7298,25 +7469,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Vancomycin</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>2ca153c6-d678-445f-8ee1-a679c933737d</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>VAN</t>
         </is>
       </c>
     </row>
@@ -7328,25 +7499,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>VITD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Vitamin D</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>040b9296-75bf-4a2d-b579-8e9148dff8cd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>VITD</t>
         </is>
       </c>
     </row>
@@ -7358,25 +7529,25 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FLU</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Flucloxacillin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>daf84ace-b41b-45e2-8fcd-c138e8db79e2</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FLU</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -7388,25 +7559,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PCM</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paracetamol</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>c2d4e43c-293a-4377-8d40-e70911ac6212</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PCM</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -7418,115 +7589,115 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mero</t>
+          <t>FLU</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Meropenem</t>
+          <t>Flucloxacillin</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>549ecb6a-9253-4fb6-b322-a0768a0994e2</t>
+          <t>daf84ace-b41b-45e2-8fcd-c138e8db79e2</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mero</t>
+          <t>FLU</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LMP</t>
+          <t>PCM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Last Menstrual Period (LMP)</t>
+          <t>Paracetamol</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>629168d6-09a0-4e45-83f7-f96ca3574cd6</t>
+          <t>c2d4e43c-293a-4377-8d40-e70911ac6212</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LMP</t>
+          <t>PCM</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mero</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fundal height</t>
+          <t>Meropenem</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>37ceb6c2-92b9-4b6d-8565-019a630efc7f</t>
+          <t>549ecb6a-9253-4fb6-b322-a0768a0994e2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mero</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>methodestgest</t>
+          <t>medsgiven</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>AZT3TC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>Zidolam (AZT and 3TC)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>caa7321e-473a-41bb-98d0-fdaf3298bf81</t>
+          <t>2f8946b7-668c-4eca-aef7-217c7378a4f3</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>USS</t>
+          <t>AZT3TC</t>
         </is>
       </c>
     </row>
@@ -7538,25 +7709,25 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EUSS</t>
+          <t>LMP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Early Ultrasound (less than 14 weeks)</t>
+          <t>Last Menstrual Period (LMP)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>987225eb-b0a5-47ca-833f-f023e6dc702e</t>
+          <t>629168d6-09a0-4e45-83f7-f96ca3574cd6</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EUSS</t>
+          <t>LMP</t>
         </is>
       </c>
     </row>
@@ -7568,25 +7739,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IVF</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IVF pregnancy</t>
+          <t>Fundal height</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>5b484c0b-8184-40fe-b159-1c83cd045f06</t>
+          <t>37ceb6c2-92b9-4b6d-8565-019a630efc7f</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>IVF</t>
+          <t>FH</t>
         </is>
       </c>
     </row>
@@ -7598,25 +7769,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>USS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>USS</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>caa7321e-473a-41bb-98d0-fdaf3298bf81</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>USS</t>
         </is>
       </c>
     </row>
@@ -7628,25 +7799,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>EUSS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Early Ultrasound (less than 14 weeks)</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>987225eb-b0a5-47ca-833f-f023e6dc702e</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>EUSS</t>
         </is>
       </c>
     </row>
@@ -7658,115 +7829,115 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MatSc</t>
+          <t>IVF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maturity score</t>
+          <t>IVF pregnancy</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>26812489-9724-40bf-a53b-8539118af5c8</t>
+          <t>5b484c0b-8184-40fe-b159-1c83cd045f06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MatSc</t>
+          <t>IVF</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spontaneous Vaginal Delivery</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3aea8950-9c6a-48fb-af0b-14523b9a69d8</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Vacuum extraction</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1ddc4820-41ef-49d5-aa4e-69da387cb21d</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>methodestgest</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MatSc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Forceps extraction</t>
+          <t>Maturity score</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01594970-3c95-4fbf-9a73-8beb14281ecd</t>
+          <t>26812489-9724-40bf-a53b-8539118af5c8</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MatSc</t>
         </is>
       </c>
     </row>
@@ -7778,25 +7949,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Elective Ceasarian Section (ELCS)</t>
+          <t>Spontaneous Vaginal Delivery</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>6d8ce857-9f83-40c6-9be3-eac23212e8e6</t>
+          <t>3aea8950-9c6a-48fb-af0b-14523b9a69d8</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SVD</t>
         </is>
       </c>
     </row>
@@ -7808,25 +7979,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Emergency Ceasarian Section (EMCS)</t>
+          <t>Vacuum extraction</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>e68a354c-7aa7-46eb-b5f2-79ba58cdec92</t>
+          <t>1ddc4820-41ef-49d5-aa4e-69da387cb21d</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7838,25 +8009,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Breech extraction (vaginal)</t>
+          <t>Forceps extraction</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>fe3efc4e-3c92-4515-860b-90de2ba627e2</t>
+          <t>01594970-3c95-4fbf-9a73-8beb14281ecd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7868,25 +8039,25 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Induced Vaginal Delivery</t>
+          <t>Elective Ceasarian Section (ELCS)</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2200ef02-8c6f-4fed-89f4-c1ec92adc8b4</t>
+          <t>6d8ce857-9f83-40c6-9be3-eac23212e8e6</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7898,25 +8069,25 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Elective Caesarean Section (ELCS)</t>
+          <t>Emergency Ceasarian Section (EMCS)</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>08ca9190-6f91-40d7-a01e-1364a362a1ca</t>
+          <t>e68a354c-7aa7-46eb-b5f2-79ba58cdec92</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7928,25 +8099,25 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Emergency Caesarean Section (EMCS)</t>
+          <t>Breech extraction (vaginal)</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1346607d-1f34-4e24-9085-317c75991a64</t>
+          <t>fe3efc4e-3c92-4515-860b-90de2ba627e2</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -7958,25 +8129,25 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Elective Caesarian Section (ELCS)</t>
+          <t>Induced Vaginal Delivery</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6779d3ec-47f0-4a65-b206-5c3047f777a9</t>
+          <t>2200ef02-8c6f-4fed-89f4-c1ec92adc8b4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -7988,25 +8159,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Emergency Caesarian Section (EMCS)</t>
+          <t>Elective Caesarean Section (ELCS)</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>d3471b13-198e-40d4-9b9f-679098db708b</t>
+          <t>08ca9190-6f91-40d7-a01e-1364a362a1ca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8018,25 +8189,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spontaneous vaginal delivery</t>
+          <t>Emergency Caesarean Section (EMCS)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>9c688b11-b2f2-4fd2-85e8-95752e0c5bf8</t>
+          <t>1346607d-1f34-4e24-9085-317c75991a64</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8048,25 +8219,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IVD</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Induced vaginal delivery</t>
+          <t>Elective Caesarian Section (ELCS)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>82c893e6-fa9e-49c1-960a-b6327db444fa</t>
+          <t>6779d3ec-47f0-4a65-b206-5c3047f777a9</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IVD</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8078,25 +8249,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Emergency Caesarean section</t>
+          <t>Emergency Caesarian Section (EMCS)</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>fa2fd7c3-100a-4cb8-9c67-de0d4c071ed6</t>
+          <t>d3471b13-198e-40d4-9b9f-679098db708b</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8108,25 +8279,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ElCS</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Elective Caesarean section</t>
+          <t>Spontaneous vaginal delivery</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>430569c0-e3d6-4a9e-a08e-9a6a025e9e08</t>
+          <t>9c688b11-b2f2-4fd2-85e8-95752e0c5bf8</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ElCS</t>
+          <t>SVD</t>
         </is>
       </c>
     </row>
@@ -8138,25 +8309,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Vent</t>
+          <t>IVD</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ventouse</t>
+          <t>Induced vaginal delivery</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>3165f6fb-49fc-4d49-9106-21b11a5abf72</t>
+          <t>82c893e6-fa9e-49c1-960a-b6327db444fa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vent</t>
+          <t>IVD</t>
         </is>
       </c>
     </row>
@@ -8168,25 +8339,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>For</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Forceps</t>
+          <t>Emergency Caesarean section</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>8fe2997a-1171-4321-aa84-59554fb03289</t>
+          <t>fa2fd7c3-100a-4cb8-9c67-de0d4c071ed6</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>For</t>
+          <t>ECS</t>
         </is>
       </c>
     </row>
@@ -8198,115 +8369,115 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ElCS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Instrumental Delivery</t>
+          <t>Elective Caesarean section</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>3ef78a13-e3ea-4986-8612-bd929fc3bc4b</t>
+          <t>430569c0-e3d6-4a9e-a08e-9a6a025e9e08</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ElCS</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Vent</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Discharged</t>
+          <t>Ventouse</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
+          <t>3165f6fb-49fc-4d49-9106-21b11a5abf72</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Vent</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>For</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Death (at LESS than 24 hrs of age)</t>
+          <t>Forceps</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
+          <t>8fe2997a-1171-4321-aa84-59554fb03289</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>For</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Death (at MORE than 24 hrs of age)</t>
+          <t>Instrumental Delivery</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
+          <t>3ef78a13-e3ea-4986-8612-bd929fc3bc4b</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -8318,25 +8489,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Discharged</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
+          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -8348,25 +8519,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Absconded</t>
+          <t>Death (at LESS than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
+          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
     </row>
@@ -8378,25 +8549,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Transferred to other ward</t>
+          <t>Death (at MORE than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
+          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
     </row>
@@ -8408,25 +8579,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
+          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DDA</t>
         </is>
       </c>
     </row>
@@ -8438,25 +8609,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Absconded</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
+          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>ABS</t>
         </is>
       </c>
     </row>
@@ -8468,25 +8639,25 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Discharge on Palliative Care</t>
+          <t>Transferred to other ward</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
+          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -8498,25 +8669,25 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
+          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>TRH</t>
         </is>
       </c>
     </row>
@@ -8528,25 +8699,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brought in dead</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
+          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>DCR</t>
         </is>
       </c>
     </row>
@@ -8558,25 +8729,25 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DPC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stillbirth</t>
+          <t>Discharge on Palliative Care</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
+          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DPC</t>
         </is>
       </c>
     </row>
@@ -8588,25 +8759,25 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>NND</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Discharged against medical advice</t>
+          <t>Died</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
+          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>NND</t>
         </is>
       </c>
     </row>
@@ -8618,25 +8789,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Live Birth</t>
+          <t>Brought in dead</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
+          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BID</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8819,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Early Neonatal Death</t>
+          <t>Stillbirth</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
+          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STB</t>
         </is>
       </c>
     </row>
@@ -8678,25 +8849,25 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stillbirth Macerated</t>
+          <t>Discharged against medical advice</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
+          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>DAMA</t>
         </is>
       </c>
     </row>
@@ -8708,25 +8879,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stillbirth Fresh</t>
+          <t>Live Birth</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
+          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
@@ -8738,25 +8909,25 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>ENND</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
+          <t>Early Neonatal Death</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
+          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>ENND</t>
         </is>
       </c>
     </row>
@@ -8773,15 +8944,15 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Stillbirth Mascerated</t>
+          <t>Stillbirth Macerated</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
+          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8798,25 +8969,25 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBF</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Miscarriage - death before 22 weeks' gestation</t>
+          <t>Stillbirth Fresh</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
+          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBF</t>
         </is>
       </c>
     </row>
@@ -8828,115 +8999,115 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Transferred to another ward (example: paediatric ward)</t>
+          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
+          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>Stillbirth Mascerated</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>e04ff02c-1286-40a2-a985-ad56a7b238fb</t>
+          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>Miscarriage - death before 22 weeks' gestation</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>de50fd8f-89b4-4e08-8d22-0ad82ec9e0e4</t>
+          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Brow</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>Transferred to another ward (example: paediatric ward)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>7c072e4f-8070-4b46-b715-a31b4c37dd1c</t>
+          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Breech</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -8948,25 +9119,25 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>15e12253-f7fc-4b3b-90b1-6cb0efe4bc56</t>
+          <t>e04ff02c-1286-40a2-a985-ad56a7b238fb</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Vertex</t>
         </is>
       </c>
     </row>
@@ -8978,115 +9149,115 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>Brow</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brow</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>de50fd8f-89b4-4e08-8d22-0ad82ec9e0e4</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>Brow</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>Breech</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Foetal Distress</t>
+          <t>Breech</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>e5304e03-7867-44a7-8570-8957e4c97915</t>
+          <t>7c072e4f-8070-4b46-b715-a31b4c37dd1c</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>Breech</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pres</t>
+          <t>Face</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Malpresentation (e.g. breech)</t>
+          <t>Face</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>d4bbfcc5-355a-4431-81a9-89664d5e38bd</t>
+          <t>15e12253-f7fc-4b3b-90b1-6cb0efe4bc56</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pres</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Scar</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Previous scar(s)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>b59e307e-3bcd-43fb-a203-1b389c4de0a3</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Scar</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
@@ -9098,25 +9269,25 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Eclampsia</t>
+          <t>Foetal Distress</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>79230ad0-5a50-4bfe-a699-1777f4b221f3</t>
+          <t>e5304e03-7867-44a7-8570-8957e4c97915</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FD</t>
         </is>
       </c>
     </row>
@@ -9128,25 +9299,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Pres</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Pre-Eclampsia</t>
+          <t>Malpresentation (e.g. breech)</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>da963f3e-55cc-4c78-8a96-1857368a46a6</t>
+          <t>d4bbfcc5-355a-4431-81a9-89664d5e38bd</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Pres</t>
         </is>
       </c>
     </row>
@@ -9158,25 +9329,25 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>Scar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Fibroids</t>
+          <t>Previous scar(s)</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>3a4978c4-8cf6-42c4-9112-c842239c440b</t>
+          <t>b59e307e-3bcd-43fb-a203-1b389c4de0a3</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>Scar</t>
         </is>
       </c>
     </row>
@@ -9188,25 +9359,25 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Big Fundus</t>
+          <t>Eclampsia</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>8f4e1cfc-2ccd-41db-bf2c-055ab1e9ba05</t>
+          <t>79230ad0-5a50-4bfe-a699-1777f4b221f3</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -9218,25 +9389,25 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Mult</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Multiple gestation</t>
+          <t>Pre-Eclampsia</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>f5a66afc-8878-448d-82cc-17b5dd56945f</t>
+          <t>da963f3e-55cc-4c78-8a96-1857368a46a6</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mult</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
@@ -9248,25 +9419,25 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prolonged labour</t>
+          <t>Fibroids</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>c4be4934-627c-49aa-b684-78bc4de63954</t>
+          <t>3a4978c4-8cf6-42c4-9112-c842239c440b</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Fi</t>
         </is>
       </c>
     </row>
@@ -9278,25 +9449,25 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Fund</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Post Term</t>
+          <t>Big Fundus</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>e8e2e171-8b87-4f36-8d5d-e2b89e8dadfb</t>
+          <t>8f4e1cfc-2ccd-41db-bf2c-055ab1e9ba05</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Fund</t>
         </is>
       </c>
     </row>
@@ -9308,25 +9479,25 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>Mult</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cephalopelvic Disproportion</t>
+          <t>Multiple gestation</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>02f990a6-3622-45b8-aaa5-654c8686b180</t>
+          <t>f5a66afc-8878-448d-82cc-17b5dd56945f</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>Mult</t>
         </is>
       </c>
     </row>
@@ -9338,132 +9509,132 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Prolonged labour</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ca00cdbe-c4c3-4dff-a5de-173001fbc6fd</t>
+          <t>c4be4934-627c-49aa-b684-78bc4de63954</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>Pr</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Booked</t>
+          <t>Post Term</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6271a881-1012-4528-b6b8-b0bf9f15256e</t>
+          <t>e8e2e171-8b87-4f36-8d5d-e2b89e8dadfb</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Unbooked</t>
+          <t>Cephalopelvic Disproportion</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2258182f-734a-494d-a6a2-0768d0eac104</t>
+          <t>02f990a6-3622-45b8-aaa5-654c8686b180</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>CPD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>8e1b1709-6e24-45f1-9b26-910e0439ccdf</t>
+          <t>ca00cdbe-c4c3-4dff-a5de-173001fbc6fd</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Stim</t>
+          <t>Bkd</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Stimulation</t>
+          <t>Booked</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -9471,29 +9642,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ca33aac1-408e-45d2-895d-4c1bdce1a60f</t>
+          <t>6271a881-1012-4528-b6b8-b0bf9f15256e</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Stim</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Suc</t>
+          <t>Ubkd</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Suctioning</t>
+          <t>Unbooked</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -9501,29 +9672,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>14af2965-3553-4e19-b699-0e65126a2644</t>
+          <t>2258182f-734a-494d-a6a2-0768d0eac104</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Suc</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>resus</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -9531,12 +9702,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>12200c9f-ca31-4949-9799-e49c6ab4ce1d</t>
+          <t>8e1b1709-6e24-45f1-9b26-910e0439ccdf</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -9548,25 +9719,25 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BVM</t>
+          <t>Stim</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (BVM)</t>
+          <t>Stimulation</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>78cc28c2-1a13-46cd-a927-8f8a22a84dad</t>
+          <t>ca33aac1-408e-45d2-895d-4c1bdce1a60f</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>BVM</t>
+          <t>Stim</t>
         </is>
       </c>
     </row>
@@ -9578,25 +9749,25 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>Suc</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cardio Pulmonary Resuscitation (CPR)</t>
+          <t>Suctioning</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>73e4b1a6-adbb-46e6-b49b-f4d3b4140ff8</t>
+          <t>14af2965-3553-4e19-b699-0e65126a2644</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>Suc</t>
         </is>
       </c>
     </row>
@@ -9608,25 +9779,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>12200c9f-ca31-4949-9799-e49c6ab4ce1d</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>O2</t>
         </is>
       </c>
     </row>
@@ -9638,25 +9809,25 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>BVM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Bag Valve Mask Ventilation (BVM)</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
+          <t>78cc28c2-1a13-46cd-a927-8f8a22a84dad</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>BVM</t>
         </is>
       </c>
     </row>
@@ -9668,25 +9839,25 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BVM9</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (less than 10 mins)</t>
+          <t>Cardio Pulmonary Resuscitation (CPR)</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>de9112c8-6ed1-424f-9b22-53fa3311c6af</t>
+          <t>73e4b1a6-adbb-46e6-b49b-f4d3b4140ff8</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>BVM9</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -9698,25 +9869,25 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BVM10</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bag Valve Mask Ventilation (Greater than 10 mins)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>93f4c9d1-e385-4448-861f-aa46f72c78d9</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>BVM10</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
@@ -9728,25 +9899,25 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ADREN</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Adrenaline</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>b6b12b8c-1130-48ce-941c-00e677dbe903</t>
+          <t>c35e45eb-88e3-4b2e-bc34-a13654027ddc</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ADREN</t>
+          <t>Norm</t>
         </is>
       </c>
     </row>
@@ -9758,25 +9929,25 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>INTUB</t>
+          <t>BVM9</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Intubation</t>
+          <t>Bag Valve Mask Ventilation (less than 10 mins)</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1904d242-d54a-44d6-a766-1c61193b585d</t>
+          <t>de9112c8-6ed1-424f-9b22-53fa3311c6af</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>INTUB</t>
+          <t>BVM9</t>
         </is>
       </c>
     </row>
@@ -9788,25 +9959,25 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BVM10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bag Valve Mask Ventilation (Greater than 10 mins)</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ec43c412-4d4e-40d8-a8c6-36c26ebff19f</t>
+          <t>93f4c9d1-e385-4448-861f-aa46f72c78d9</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>BVM10</t>
         </is>
       </c>
     </row>
@@ -9818,115 +9989,115 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADREN</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Adrenaline</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>6094c97b-0909-4539-bb8e-aa0da0c3f3ef</t>
+          <t>b6b12b8c-1130-48ce-941c-00e677dbe903</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADREN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INTUB</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Intubation</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>4e5cdd19-28a0-4dc9-94f5-d09feb56fb18</t>
+          <t>1904d242-d54a-44d6-a766-1c61193b585d</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INTUB</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tw1</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>1st Twin</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>63af2b9c-f7ed-44ef-9991-629f4a086ab5</t>
+          <t>ec43c412-4d4e-40d8-a8c6-36c26ebff19f</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tw1</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>typebirth</t>
+          <t>resus</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tw2</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2nd Twin</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>0be1f4af-4b4f-45f8-a3e8-3daa60a95632</t>
+          <t>6094c97b-0909-4539-bb8e-aa0da0c3f3ef</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tw2</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -9938,25 +10109,25 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tr1</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>1st Triplet</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1cdcce3b-27e0-4b70-9de5-f4da25d0c793</t>
+          <t>4e5cdd19-28a0-4dc9-94f5-d09feb56fb18</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tr1</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -9968,25 +10139,25 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tr2</t>
+          <t>Tw1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2nd Triplet</t>
+          <t>1st Twin</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1d2569b0-6807-4007-93d4-965f3b56ce8d</t>
+          <t>63af2b9c-f7ed-44ef-9991-629f4a086ab5</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tr2</t>
+          <t>Tw1</t>
         </is>
       </c>
     </row>
@@ -9998,25 +10169,25 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tr3</t>
+          <t>Tw2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>3rd Triplet</t>
+          <t>2nd Twin</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>e0ca7796-b2df-47a4-9144-3a6cc74b4859</t>
+          <t>0be1f4af-4b4f-45f8-a3e8-3daa60a95632</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tr3</t>
+          <t>Tw2</t>
         </is>
       </c>
     </row>
@@ -10028,25 +10199,25 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Tr1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1st Quadruplet</t>
+          <t>1st Triplet</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>294280e4-e5e6-4160-982b-86ba5cdbde06</t>
+          <t>1cdcce3b-27e0-4b70-9de5-f4da25d0c793</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Tr1</t>
         </is>
       </c>
     </row>
@@ -10058,25 +10229,25 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Tr2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2nd Quadruplet</t>
+          <t>2nd Triplet</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>3546150a-af2b-4ced-8f25-a60c25dac62d</t>
+          <t>1d2569b0-6807-4007-93d4-965f3b56ce8d</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Tr2</t>
         </is>
       </c>
     </row>
@@ -10088,25 +10259,25 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Tr3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>3rd Quadruplet</t>
+          <t>3rd Triplet</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2b41e898-f918-4229-9390-7ea861d5ad52</t>
+          <t>e0ca7796-b2df-47a4-9144-3a6cc74b4859</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Tr3</t>
         </is>
       </c>
     </row>
@@ -10118,25 +10289,25 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>4th Quadruplet</t>
+          <t>1st Quadruplet</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>a9f55c14-30c3-43c1-9900-9631d281ab12</t>
+          <t>294280e4-e5e6-4160-982b-86ba5cdbde06</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
     </row>
@@ -10148,125 +10319,140 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Multiple birth</t>
+          <t>2nd Quadruplet</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>0b6d0d11-ef3b-4845-b57d-1dda870fb1f3</t>
+          <t>3546150a-af2b-4ced-8f25-a60c25dac62d</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>modedelivery</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spontaneous Vaginal Delivery (SVD)</t>
+          <t>3rd Quadruplet</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2b41e898-f918-4229-9390-7ea861d5ad52</t>
+        </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Q3</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Booked (legacy Y)</t>
+          <t>4th Quadruplet</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>a9f55c14-30c3-43c1-9900-9631d281ab12</t>
+        </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>typebirth</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Booked (legacy Yes)</t>
+          <t>Multiple birth</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0b6d0d11-ef3b-4845-b57d-1dda870fb1f3</t>
+        </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bkd</t>
+          <t>Twin</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>receivedantenatalcare</t>
+          <t>modedelivery</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Unbooked (legacy N)</t>
+          <t>Spontaneous Vaginal Delivery (SVD)</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10278,95 +10464,95 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Unbooked (legacy No)</t>
+          <t>Booked (legacy Y)</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ubkd</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prematurity (legacy PR)</t>
+          <t>Booked (legacy Yes)</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>Bkd</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Birth asphyxia / HIE (legacy BA)</t>
+          <t>Unbooked (legacy N)</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>diagdis1</t>
+          <t>receivedantenatalcare</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PRRDS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Premature with respiratory distress (legacy PRRDS)</t>
+          <t>Unbooked (legacy No)</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>Ubkd</t>
         </is>
       </c>
     </row>
@@ -10378,20 +10564,20 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Feeding difficulty (legacy FD)</t>
+          <t>Prematurity (legacy PR)</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>Prem</t>
         </is>
       </c>
     </row>
@@ -10403,20 +10589,20 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HIVXL</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>HIV exposed low risk (legacy HIVXL)</t>
+          <t>Birth asphyxia / HIE (legacy BA)</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIE</t>
         </is>
       </c>
     </row>
@@ -10428,20 +10614,20 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ri</t>
+          <t>PRRDS</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Sepsis risk factors (legacy Ri)</t>
+          <t>Premature with respiratory distress (legacy PRRDS)</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>PremRD</t>
         </is>
       </c>
     </row>
@@ -10453,20 +10639,20 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OCA</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other congenital abnormality (legacy OCA)</t>
+          <t>Feeding difficulty (legacy FD)</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cong</t>
+          <t>DF</t>
         </is>
       </c>
     </row>
@@ -10478,18 +10664,93 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
+          <t>HIVXL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>HIV exposed low risk (legacy HIVXL)</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>74</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>HIVLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ri</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sepsis risk factors (legacy Ri)</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>75</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OCA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Other congenital abnormality (legacy OCA)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>76</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Cong</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>diagdis1</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
           <t>BI</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Birth injury / trauma (legacy BI)</t>
         </is>
       </c>
-      <c r="D235" t="n">
-        <v>76</v>
-      </c>
-      <c r="F235" t="inlineStr">
+      <c r="D238" t="n">
+        <v>77</v>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
@@ -11151,6 +11412,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ZIM_baseline</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Categorical with no value map entries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
